--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>40549.48</v>
+        <v>41291.5</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>69258.95</v>
+        <v>68470.73</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>32386.41</v>
+        <v>32184.26</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>36616.27</v>
+        <v>36901.82</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>29029.12</v>
+        <v>29283.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2404-234-CM26</t>
+          <t>3447-1175-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>41291.5</v>
+        <v>34488.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1070620-2658-CM26</t>
+          <t>2404-528-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>68470.73</v>
+        <v>33804.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2404-285-CM26</t>
+          <t>2404-234-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>32184.26</v>
+        <v>41291.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3447-1226-CM26</t>
+          <t>1070620-2658-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>36901.82</v>
+        <v>68470.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3447-1547-CM26</t>
+          <t>2404-285-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,6 +813,128 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
+        <v>32184.26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3447-1226-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SOSAFE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>36901.82</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3447-1547-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>29283.71</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3447-1547-CM26</t>
+          <t>1305552-66-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,6 +935,67 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>50043.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3447-1547-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>29283.71</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -636,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2404-234-CM26</t>
+          <t>3447-5073-SE25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +650,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,28 +680,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>41291.5</v>
+        <v>13024.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1070620-2658-CM26</t>
+          <t>2404-234-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +730,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +745,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +760,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>68470.73</v>
+        <v>41291.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2404-285-CM26</t>
+          <t>1070620-2658-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +781,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +791,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,28 +806,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>32184.26</v>
+        <v>68470.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3447-1226-CM26</t>
+          <t>2404-285-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +841,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +856,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,28 +871,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>36901.82</v>
+        <v>32184.26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1305552-66-CM26</t>
+          <t>3447-1226-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +911,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +921,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,28 +936,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Andestic SpA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>50043.25</v>
+        <v>36901.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3447-1547-CM26</t>
+          <t>1305552-66-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +971,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +1001,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,6 +1016,71 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>50043.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3447-1547-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>29283.71</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/tarapaca.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
